--- a/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>ETCG</t>
   </si>
@@ -656,80 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +775,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -781,43 +787,46 @@
         <v>1300</v>
       </c>
       <c r="E9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>5100</v>
       </c>
       <c r="M9" s="3">
         <v>5100</v>
       </c>
       <c r="N9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -825,43 +834,46 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-4400</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-5100</v>
       </c>
       <c r="M10" s="3">
         <v>-5100</v>
       </c>
       <c r="N10" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="O10" s="3">
         <v>-1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +982,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1029,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1094,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1078,43 +1104,46 @@
         <v>1300</v>
       </c>
       <c r="E17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5100</v>
       </c>
       <c r="M17" s="3">
         <v>5100</v>
       </c>
       <c r="N17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1122,43 +1151,46 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-5100</v>
       </c>
       <c r="M18" s="3">
         <v>-5100</v>
       </c>
       <c r="N18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1207,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1184,43 +1217,46 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-11500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>57600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-140300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>157700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-393700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>164900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-158800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-110800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>523400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>96900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1299,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>56000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-141900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>155400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-395700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>162100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-163200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-115900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>518300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>95900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-39300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-141900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>155400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-395700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>162100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-163200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-115900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>518300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>95900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>56000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-141900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>155400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-395700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>162100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-163200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-115900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>518300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>95900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1769,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1712,87 +1781,93 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F32" s="3">
         <v>11500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-57600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>140300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-157700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>393700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-164900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>158800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>110800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-523400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-96900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>56000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-141900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>155400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-395700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>162100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-163200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-115900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>518300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>95900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>56000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-141900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>155400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-395700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>162100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-163200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-115900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>518300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>95900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,8 +2049,9 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2008,8 +2094,11 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,8 +2141,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2096,8 +2188,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,8 +2235,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2184,8 +2282,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2228,41 +2329,44 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E47" s="3">
         <v>191200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>230500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>243400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>187300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>329200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>173900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>569500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>407500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>570600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2272,8 +2376,11 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2316,8 +2423,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2470,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2564,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,41 +2658,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E54" s="3">
         <v>191200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>230500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>243400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>187300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>329200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>173900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>569500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>407500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>570600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2580,8 +2705,11 @@
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,8 +2745,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2660,8 +2790,11 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2704,8 +2837,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2748,8 +2884,11 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2792,8 +2931,11 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,8 +2978,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2880,8 +3025,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,8 +3166,11 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3056,8 +3213,11 @@
       <c r="P66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,41 +3420,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3294,8 +3467,11 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,41 +3608,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E76" s="3">
         <v>191200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>230500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>243400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>187300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>329200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>173900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>569500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>407500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>570600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3470,8 +3655,11 @@
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>56000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-141900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>155400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-395700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>162100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-163200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-115900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>518300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>95900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3822,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3669,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,8 +4102,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3933,8 +4149,11 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4170,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4309,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4127,8 +4356,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,8 +4563,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4365,8 +4610,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,8 +4657,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4451,6 +4702,9 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>ETCG</t>
   </si>
@@ -656,83 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,55 +782,61 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="3">
         <v>1300</v>
       </c>
       <c r="F9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>5100</v>
       </c>
       <c r="N9" s="3">
         <v>5100</v>
       </c>
       <c r="O9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,43 +847,46 @@
         <v>-1300</v>
       </c>
       <c r="F10" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G10" s="3">
         <v>-1400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-4400</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-5100</v>
       </c>
       <c r="N10" s="3">
         <v>-5100</v>
       </c>
       <c r="O10" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="P10" s="3">
         <v>-1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,55 +1121,59 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="E17" s="3">
         <v>1300</v>
       </c>
       <c r="F17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5100</v>
       </c>
       <c r="N17" s="3">
         <v>5100</v>
       </c>
       <c r="O17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1154,43 +1184,46 @@
         <v>-1300</v>
       </c>
       <c r="F18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-5100</v>
       </c>
       <c r="N18" s="3">
         <v>-5100</v>
       </c>
       <c r="O18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1241,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,46 +1251,49 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>64100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-38100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>57600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-140300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>157700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-393700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>164900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-158800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-110800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>523400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>96900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1339,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E23" s="3">
         <v>62800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-39300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>56000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-141900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>155400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-395700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>162100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-163200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-115900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>518300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>95900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E26" s="3">
         <v>62800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-141900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>155400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-395700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>162100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-163200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-115900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>518300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>95900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E27" s="3">
         <v>62800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>56000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-141900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>155400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-395700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>162100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-163200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-115900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>518300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>95900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1839,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1781,93 +1851,99 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-64100</v>
+      </c>
+      <c r="F32" s="3">
         <v>38100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-57600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>140300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-157700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>393700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-164900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>158800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>110800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-523400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-96900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E33" s="3">
         <v>62800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>56000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-141900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>155400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-395700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>162100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-163200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-115900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>518300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>95900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E35" s="3">
         <v>62800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>56000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-141900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>155400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-395700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>162100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-163200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-115900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>518300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>95900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,8 +2136,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2097,8 +2184,11 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2144,8 +2234,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2191,8 +2284,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,8 +2334,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2285,8 +2384,11 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2332,44 +2434,47 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>391100</v>
+      </c>
+      <c r="E47" s="3">
         <v>254000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>191200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>230500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>243400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>187300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>329200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>173900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>569500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>407500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>570600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2379,8 +2484,11 @@
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2426,8 +2534,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,44 +2784,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>391100</v>
+      </c>
+      <c r="E54" s="3">
         <v>254000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>191200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>230500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>243400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>187300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>329200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>173900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>569500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>407500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>570600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2708,8 +2834,11 @@
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,8 +2876,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2793,8 +2924,11 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2840,8 +2974,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2887,8 +3024,11 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2934,8 +3074,11 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2981,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,8 +3324,11 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3216,8 +3374,11 @@
       <c r="Q66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,44 +3594,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3470,8 +3644,11 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,44 +3794,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>391100</v>
+      </c>
+      <c r="E76" s="3">
         <v>254000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>191200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>230500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>243400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>187300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>329200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>173900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>569500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>407500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>570600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3658,8 +3844,11 @@
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E81" s="3">
         <v>62800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>56000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-141900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>155400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-395700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>162100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-163200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-115900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>518300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>95900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,8 +4319,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4152,8 +4369,11 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,8 +4539,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4359,8 +4589,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,8 +4809,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4613,8 +4859,11 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4660,8 +4909,11 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4705,6 +4957,9 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>ETCG</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,8 +789,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -794,49 +801,52 @@
         <v>2000</v>
       </c>
       <c r="E9" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="3">
         <v>1300</v>
       </c>
       <c r="G9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>5100</v>
       </c>
       <c r="O9" s="3">
         <v>5100</v>
       </c>
       <c r="P9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,49 +854,52 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
-        <v>-1300</v>
+        <v>-2000</v>
       </c>
       <c r="F10" s="3">
         <v>-1300</v>
       </c>
       <c r="G10" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H10" s="3">
         <v>-1400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-4400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>-5100</v>
       </c>
       <c r="O10" s="3">
         <v>-5100</v>
       </c>
       <c r="P10" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,8 +1148,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1131,49 +1158,52 @@
         <v>2000</v>
       </c>
       <c r="E17" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="F17" s="3">
         <v>1300</v>
       </c>
       <c r="G17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5100</v>
       </c>
       <c r="O17" s="3">
         <v>5100</v>
       </c>
       <c r="P17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,49 +1211,52 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-1300</v>
+        <v>-2000</v>
       </c>
       <c r="F18" s="3">
         <v>-1300</v>
       </c>
       <c r="G18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-5100</v>
       </c>
       <c r="O18" s="3">
         <v>-5100</v>
       </c>
       <c r="P18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1251,49 +1285,52 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>139200</v>
+      </c>
+      <c r="F20" s="3">
         <v>64100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-38100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>57600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-140300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>157700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-393700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>164900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-158800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-110800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>523400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>96900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E23" s="3">
         <v>137200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>62800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>56000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-141900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>155400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-395700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>162100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-163200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-115900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>518300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>95900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E26" s="3">
         <v>137200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>62800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-141900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>155400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-395700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>162100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-163200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-115900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>518300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>95900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E27" s="3">
         <v>137200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>56000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-141900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>155400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-395700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>162100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-163200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-115900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>518300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>95900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1851,99 +1921,105 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-64100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>38100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-57600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>140300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-157700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>393700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-164900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>158800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>110800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-523400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-96900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E33" s="3">
         <v>137200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>62800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>56000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-141900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>155400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-395700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>162100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-163200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-115900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>518300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>95900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E35" s="3">
         <v>137200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>62800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>56000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-141900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>155400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-395700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>162100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-163200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-115900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>518300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>95900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,8 +2223,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2187,8 +2274,11 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,8 +2327,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2287,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2387,8 +2486,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2437,46 +2539,49 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>268700</v>
+      </c>
+      <c r="E47" s="3">
         <v>391100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>254000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>191200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>230500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>243400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>187300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>329200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>173900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>569500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>407500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>570600</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -2487,8 +2592,11 @@
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2537,8 +2645,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,46 +2910,49 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>268700</v>
+      </c>
+      <c r="E54" s="3">
         <v>391100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>254000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>191200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>230500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>243400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>187300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>329200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>173900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>569500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>407500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>570600</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
@@ -2837,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,8 +3007,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2927,8 +3058,11 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,8 +3111,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3027,8 +3164,11 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3077,8 +3217,11 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3127,8 +3270,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,8 +3482,11 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3377,8 +3535,11 @@
       <c r="R66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,46 +3768,49 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7800</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
@@ -3647,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,46 +3980,49 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>268700</v>
+      </c>
+      <c r="E76" s="3">
         <v>391100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>191200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>230500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>243400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>187300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>329200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>173900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>569500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>407500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>570600</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
@@ -3847,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-122400</v>
+      </c>
+      <c r="E81" s="3">
         <v>137200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>62800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>56000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-141900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>155400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-395700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>162100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-163200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-115900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>518300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>95900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,8 +4536,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4372,8 +4589,11 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,8 +5055,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4862,8 +5108,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,8 +5161,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4960,6 +5212,9 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>
